--- a/apps/pit/Pinch.xlsx
+++ b/apps/pit/Pinch.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucdavis365-my.sharepoint.com/personal/ovkhan_ucdavis_edu/Documents/git_mac/IAC-Decarb-Tools-Dev/apps/pit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucdavis365-my.sharepoint.com/personal/ovkhan_ucdavis_edu/Documents/git_mac/IAC-Decarb-Tools/apps/pit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{81CF5E86-67A3-45B0-A16D-975B2F380700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C84C059A-EC31-2B41-A794-D10A5B337288}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{B31807A1-47A3-490E-A617-6BC1D06FD2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0A892D-BFA0-3740-B0FB-E9590AC001C3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17700" activeTab="1" xr2:uid="{441EF13B-B6FE-4A4F-997B-7879B27FE7C5}"/>
+    <workbookView xWindow="16660" yWindow="4460" windowWidth="30240" windowHeight="17780" activeTab="1" xr2:uid="{441EF13B-B6FE-4A4F-997B-7879B27FE7C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinch " sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="Streams" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="5" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
   <si>
     <t>Pinch Analysis: Thermodynamic and Techno-economic HX Potential</t>
   </si>
@@ -250,10 +251,43 @@
     <t>Tout</t>
   </si>
   <si>
+    <t>mCp</t>
+  </si>
+  <si>
     <t>°F</t>
   </si>
   <si>
+    <t>°C</t>
+  </si>
+  <si>
     <t>MMBtu/hr</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>MJ/hr</t>
+  </si>
+  <si>
+    <t>MMBtu/°F-hr</t>
+  </si>
+  <si>
+    <t>MW/°C</t>
+  </si>
+  <si>
+    <t>MJ/°C-hr</t>
+  </si>
+  <si>
+    <t>kW/°C</t>
+  </si>
+  <si>
+    <t>kJ/°C-hr</t>
+  </si>
+  <si>
+    <t>kJ/hr</t>
+  </si>
+  <si>
+    <t>kW</t>
   </si>
   <si>
     <t>Hot Water</t>
@@ -400,8 +434,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -8410,7 +8444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1A0AAF-0E70-44D7-9B8F-1923E76D95E6}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" style="16" bestFit="1" customWidth="1"/>
@@ -8418,6 +8452,7 @@
     <col min="3" max="4" width="11.5" customWidth="1"/>
     <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" x14ac:dyDescent="0.2">
@@ -8444,13 +8479,13 @@
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" s="14"/>
     </row>
@@ -8459,7 +8494,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C3" s="5">
         <v>55</v>
@@ -8467,7 +8502,7 @@
       <c r="D3" s="5">
         <v>130</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="18">
         <v>11.9808</v>
       </c>
       <c r="F3" t="s">
@@ -8479,15 +8514,15 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>179</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>188</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="18">
         <v>1.75</v>
       </c>
       <c r="F4" t="s">
@@ -8499,7 +8534,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>170</v>
@@ -8507,7 +8542,7 @@
       <c r="D5">
         <v>130</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <v>0.59698069545037169</v>
       </c>
       <c r="F5" t="s">
@@ -8519,7 +8554,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C6" s="5">
         <v>170</v>
@@ -8527,7 +8562,7 @@
       <c r="D6" s="5">
         <v>94.476759289787196</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <v>2.1121600565702972</v>
       </c>
       <c r="F6" t="s">
@@ -8539,7 +8574,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C7" s="5">
         <v>94.476759289787196</v>
@@ -8547,7 +8582,7 @@
       <c r="D7" s="5">
         <v>94.476759289787196</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <v>21.772125368840999</v>
       </c>
       <c r="F7" t="s">
@@ -8559,7 +8594,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C8">
         <v>75</v>
@@ -8567,12 +8602,15 @@
       <c r="D8">
         <v>50</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <v>8.67</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
       </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E9" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -8582,13 +8620,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2A331D1-F568-4B2B-98B5-813334EA5284}">
           <x14:formula1>
-            <xm:f>#REF!</xm:f>
+            <xm:f>Sheet3!$C$3:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>C2:D2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AC09B3B6-AE78-4D4A-93DE-984556E2C91D}">
           <x14:formula1>
-            <xm:f>#REF!</xm:f>
+            <xm:f>Sheet3!$F$3:$F$7</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
@@ -8596,7 +8634,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F15</xm:sqref>
+          <xm:sqref>F2 F9:F16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8605,6 +8643,88 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59316CEE-5091-4D0C-AF84-A153BD5A97B8}">
+  <dimension ref="C2:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C2" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C4" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="E6" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="E7" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF33AA2-05A8-47E9-B272-F49E875613E6}">
   <dimension ref="C2:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8625,6 +8745,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8633,7 +8759,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FA618A2FDB47E24BAEDBBD56213D2C90" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e23952f311cf1ff95f8c285772f2db25">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c0920b8cc3e49c06a3bb432624b7e4d" ns3:_="">
     <xsd:import namespace="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882"/>
@@ -8823,13 +8949,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36349EE4-8743-4275-95B0-0EE709FF3902}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1739E893-96A1-43F3-B0F5-E6FE85C79CA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -8837,7 +8973,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55532D3E-4DE8-4FB1-A313-4A752DC6EC93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8853,20 +8989,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36349EE4-8743-4275-95B0-0EE709FF3902}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/apps/pit/Pinch.xlsx
+++ b/apps/pit/Pinch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucdavis365-my.sharepoint.com/personal/ovkhan_ucdavis_edu/Documents/git_mac/IAC-Decarb-Tools/apps/pit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucdavis365-my.sharepoint.com/personal/ovkhan_ucdavis_edu/Documents/git_mac/IAC-Decarb-Tools-Dev/apps/pit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{B31807A1-47A3-490E-A617-6BC1D06FD2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0A892D-BFA0-3740-B0FB-E9590AC001C3}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{B31807A1-47A3-490E-A617-6BC1D06FD2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D5500CF-2AE4-EF47-B22C-AEB24D5A8731}"/>
   <bookViews>
-    <workbookView xWindow="16660" yWindow="4460" windowWidth="30240" windowHeight="17780" activeTab="1" xr2:uid="{441EF13B-B6FE-4A4F-997B-7879B27FE7C5}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="1" xr2:uid="{441EF13B-B6FE-4A4F-997B-7879B27FE7C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinch " sheetId="2" state="hidden" r:id="rId1"/>
@@ -8503,7 +8503,7 @@
         <v>130</v>
       </c>
       <c r="E3" s="18">
-        <v>11.9808</v>
+        <v>11.98</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -8543,7 +8543,7 @@
         <v>130</v>
       </c>
       <c r="E5" s="18">
-        <v>0.59698069545037169</v>
+        <v>0.6</v>
       </c>
       <c r="F5" t="s">
         <v>42</v>
@@ -8563,7 +8563,7 @@
         <v>94.476759289787196</v>
       </c>
       <c r="E6" s="18">
-        <v>2.1121600565702972</v>
+        <v>2.11</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -8583,7 +8583,7 @@
         <v>94.476759289787196</v>
       </c>
       <c r="E7" s="18">
-        <v>21.772125368840999</v>
+        <v>21.77</v>
       </c>
       <c r="F7" t="s">
         <v>42</v>
@@ -8617,7 +8617,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2A331D1-F568-4B2B-98B5-813334EA5284}">
           <x14:formula1>
             <xm:f>Sheet3!$C$3:$C$4</xm:f>
@@ -8745,21 +8745,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FA618A2FDB47E24BAEDBBD56213D2C90" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e23952f311cf1ff95f8c285772f2db25">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c0920b8cc3e49c06a3bb432624b7e4d" ns3:_="">
     <xsd:import namespace="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882"/>
@@ -8949,31 +8934,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36349EE4-8743-4275-95B0-0EE709FF3902}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1739E893-96A1-43F3-B0F5-E6FE85C79CA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55532D3E-4DE8-4FB1-A313-4A752DC6EC93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8989,4 +8965,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1739E893-96A1-43F3-B0F5-E6FE85C79CA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36349EE4-8743-4275-95B0-0EE709FF3902}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7f8b2b10-a8de-45fe-8018-6d7fcf2dd882"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>